--- a/data/trans_dic/P05B_R-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P05B_R-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,8%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,99; 5,26</t>
+          <t>1,96; 5,21</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,57; 5,01</t>
+          <t>1,57; 5,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,47; 3,17</t>
+          <t>0,47; 3,25</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1,03; 4,01</t>
+          <t>0,99; 3,89</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>2,61; 7,59</t>
+          <t>2,51; 7,3</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,68</t>
+          <t>0,28; 2,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,28; 2,57</t>
+          <t>0,28; 2,81</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,27</t>
+          <t>0,77; 3,14</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2,5; 5,15</t>
+          <t>2,63; 5,32</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1,19; 3,4</t>
+          <t>1,16; 3,48</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0,53; 2,24</t>
+          <t>0,53; 2,3</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,15; 3,1</t>
+          <t>1,05; 2,93</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,08%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,69; 5,85</t>
+          <t>1,49; 5,66</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,75; 4,06</t>
+          <t>0,77; 4,14</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,45</t>
+          <t>0,0; 1,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,13; 1,61</t>
+          <t>0,12; 1,46</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>1,99; 6,33</t>
+          <t>1,88; 5,72</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,88; 4,08</t>
+          <t>0,87; 4,23</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 4,05</t>
+          <t>0,84; 3,97</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0,93; 3,94</t>
+          <t>0,78; 3,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 5,08</t>
+          <t>2,28; 5,01</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,1; 3,41</t>
+          <t>1,09; 3,43</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,54; 2,25</t>
+          <t>0,59; 2,46</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0,58; 2,03</t>
+          <t>0,56; 1,85</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -997,32 +997,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,08; 3,45</t>
+          <t>1,18; 3,72</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,32; 1,94</t>
+          <t>0,32; 1,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,15; 1,99</t>
+          <t>0,15; 2,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 1,89</t>
+          <t>0,38; 2,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,11; 10,71</t>
+          <t>3,2; 11,4</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 3,55</t>
+          <t>0,38; 3,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
@@ -1032,27 +1032,27 @@
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,1; 2,66</t>
+          <t>0,23; 2,46</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>1,96; 4,51</t>
+          <t>1,93; 4,55</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 1,74</t>
+          <t>0,47; 1,81</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,46</t>
+          <t>0,12; 1,79</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,68</t>
+          <t>0,44; 1,98</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,87%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,02%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,55</t>
+          <t>2,29; 4,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 2,77</t>
+          <t>1,12; 2,69</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,34; 3,13</t>
+          <t>1,44; 3,12</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,46; 1,81</t>
+          <t>0,4; 1,57</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>3,32; 6,26</t>
+          <t>3,22; 6,26</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,53; 3,94</t>
+          <t>1,56; 3,97</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,64; 4,2</t>
+          <t>1,63; 3,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0,42; 1,7</t>
+          <t>0,69; 1,9</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,02; 4,83</t>
+          <t>2,96; 4,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 2,76</t>
+          <t>1,46; 2,91</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,06</t>
+          <t>1,73; 3,15</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 1,5</t>
+          <t>0,67; 1,53</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,24%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 3,85</t>
+          <t>0,95; 3,9</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,26</t>
+          <t>0,39; 2,36</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0,76; 3,16</t>
+          <t>0,8; 2,96</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,41; 2,24</t>
+          <t>0,42; 2,17</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>3,44; 7,24</t>
+          <t>3,32; 6,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,27</t>
+          <t>0,41; 2,25</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 2,97</t>
+          <t>1,03; 3,15</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 2,21</t>
+          <t>0,89; 2,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2,72; 5,16</t>
+          <t>2,67; 5,29</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>0,55; 1,84</t>
+          <t>0,53; 1,78</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,59</t>
+          <t>1,12; 2,57</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>0,82; 1,93</t>
+          <t>0,82; 1,8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,48%</t>
         </is>
       </c>
     </row>
@@ -1417,17 +1417,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>1,5; 6,24</t>
+          <t>1,74; 6,31</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0,71; 3,97</t>
+          <t>0,71; 4,01</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,75</t>
+          <t>0,0; 1,83</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -1437,42 +1437,42 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>3,52; 5,92</t>
+          <t>3,6; 6,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,98; 2,59</t>
+          <t>1,0; 2,5</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>1,96; 3,92</t>
+          <t>1,85; 4,01</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>0,33; 1,25</t>
+          <t>0,29; 1,17</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>3,46; 5,7</t>
+          <t>3,42; 5,53</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,5</t>
+          <t>1,03; 2,5</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1,55; 3,31</t>
+          <t>1,55; 3,4</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0,23; 0,92</t>
+          <t>0,24; 0,9</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>2,4; 3,61</t>
+          <t>2,38; 3,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>1,27; 2,22</t>
+          <t>1,22; 2,18</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1,02; 1,88</t>
+          <t>0,99; 1,85</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,67; 1,45</t>
+          <t>0,69; 1,34</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,01; 5,49</t>
+          <t>4,07; 5,47</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,19; 2,09</t>
+          <t>1,21; 2,1</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>1,68; 2,68</t>
+          <t>1,7; 2,69</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,87; 1,53</t>
+          <t>0,95; 1,58</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3,41; 4,3</t>
+          <t>3,38; 4,35</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>1,36; 1,99</t>
+          <t>1,35; 1,99</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>1,47; 2,15</t>
+          <t>1,45; 2,12</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>0,85; 1,39</t>
+          <t>0,89; 1,38</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10868</t>
+          <t>11171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>7259</t>
+          <t>7474</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18127</t>
+          <t>18645</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>9365; 24793</t>
+          <t>9254; 24559</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>6821; 21755</t>
+          <t>6813; 22231</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2024; 13608</t>
+          <t>2036; 13935</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5212; 20224</t>
+          <t>5461; 21386</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8011; 23272</t>
+          <t>7708; 22377</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>876; 8417</t>
+          <t>884; 7368</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>978; 8882</t>
+          <t>974; 9699</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>3371; 14546</t>
+          <t>3714; 15217</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>19486; 40086</t>
+          <t>20478; 41393</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8890; 25482</t>
+          <t>8651; 26049</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>4112; 17357</t>
+          <t>4102; 17808</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10932; 29356</t>
+          <t>10872; 30307</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2410</t>
+          <t>2529</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>7271</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>9647</t>
+          <t>9800</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>6200; 21448</t>
+          <t>5483; 20756</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>3121; 16875</t>
+          <t>3188; 17218</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 9220</t>
+          <t>0; 6478</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>580; 7249</t>
+          <t>578; 7034</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7398; 23528</t>
+          <t>7008; 21255</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2985; 13802</t>
+          <t>2956; 14302</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3170; 15086</t>
+          <t>3141; 14788</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3553; 15047</t>
+          <t>3296; 13999</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>16311; 37507</t>
+          <t>16815; 37018</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8258; 25695</t>
+          <t>8184; 25841</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4056; 16866</t>
+          <t>4399; 18435</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4828; 16887</t>
+          <t>5098; 16712</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1250</t>
+          <t>1802</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>6121</t>
+          <t>6662</t>
         </is>
       </c>
     </row>
@@ -2343,32 +2343,32 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5860; 18707</t>
+          <t>6408; 20183</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1989; 12167</t>
+          <t>1993; 11128</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>795; 10388</t>
+          <t>794; 10606</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>661; 12652</t>
+          <t>1789; 11442</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>5219; 17976</t>
+          <t>5366; 19134</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>980; 9082</t>
+          <t>964; 8431</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -2378,27 +2378,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>164; 4418</t>
+          <t>428; 4585</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>13927; 32001</t>
+          <t>13735; 32282</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3960; 15402</t>
+          <t>4149; 15970</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>788; 10034</t>
+          <t>793; 12299</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>1636; 14029</t>
+          <t>2896; 13062</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>9972</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>9599</t>
+          <t>10434</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>19571</t>
+          <t>20288</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>29794; 56280</t>
+          <t>28359; 56135</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>12770; 32022</t>
+          <t>12924; 31127</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15336; 35761</t>
+          <t>16442; 35725</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4755; 18665</t>
+          <t>4567; 17779</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>23680; 44742</t>
+          <t>22975; 44722</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11710; 30198</t>
+          <t>11977; 30381</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13461; 34496</t>
+          <t>13363; 32017</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>4102; 16631</t>
+          <t>5920; 16377</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>58853; 94169</t>
+          <t>57687; 91271</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>27789; 53103</t>
+          <t>28053; 56008</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>33889; 60079</t>
+          <t>33913; 61861</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12074; 30178</t>
+          <t>13330; 30454</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>5284</t>
+          <t>5275</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16850</t>
+          <t>17257</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3387; 13507</t>
+          <t>3343; 13689</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>1965; 11557</t>
+          <t>1976; 12030</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4694; 19595</t>
+          <t>4950; 18375</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>1947; 10631</t>
+          <t>2366; 12290</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>19496; 41085</t>
+          <t>18826; 39623</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2882; 17186</t>
+          <t>3136; 17028</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7294; 21921</t>
+          <t>7592; 23187</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>6941; 18538</t>
+          <t>7353; 18478</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24962; 47313</t>
+          <t>24534; 48561</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6928; 23393</t>
+          <t>6742; 22636</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>15329; 35209</t>
+          <t>15198; 34940</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10756; 25332</t>
+          <t>11484; 25059</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5193</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>4981</t>
+          <t>5193</t>
         </is>
       </c>
     </row>
@@ -2967,17 +2967,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4485; 18597</t>
+          <t>5184; 18809</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1878; 10483</t>
+          <t>1864; 10582</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 5020</t>
+          <t>0; 5239</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -2987,42 +2987,42 @@
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>43904; 73941</t>
+          <t>44979; 74951</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>10796; 28491</t>
+          <t>10988; 27542</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21048; 42181</t>
+          <t>19923; 43083</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>2474; 9469</t>
+          <t>2473; 9887</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>53602; 88143</t>
+          <t>52847; 85544</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15381; 34102</t>
+          <t>14120; 34172</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>21034; 45044</t>
+          <t>21130; 46251</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>2340; 9248</t>
+          <t>2591; 9734</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>33689</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>41891</t>
+          <t>44156</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>75296</t>
+          <t>77845</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>78329; 118021</t>
+          <t>77853; 116282</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>43128; 75620</t>
+          <t>41539; 74241</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>34289; 63364</t>
+          <t>33601; 62429</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22536; 48901</t>
+          <t>23609; 45997</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>135423; 185375</t>
+          <t>137548; 184655</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>42160; 73973</t>
+          <t>42774; 74363</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>58955; 94201</t>
+          <t>59905; 94765</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>31150; 54574</t>
+          <t>34380; 57225</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>226712; 285587</t>
+          <t>224398; 288975</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94176; 138454</t>
+          <t>93706; 137973</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101367; 148431</t>
+          <t>100146; 146452</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>59216; 96188</t>
+          <t>62563; 97433</t>
         </is>
       </c>
     </row>
